--- a/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
   <si>
     <t>Property</t>
   </si>
@@ -67,21 +67,6 @@
   </si>
   <si>
     <t>Publisher</t>
-  </si>
-  <si>
-    <t>ANS</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>ANS (https://esante.gouv.fr)</t>
-  </si>
-  <si>
-    <t>Jurisdiction</t>
-  </si>
-  <si>
-    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -263,7 +248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -346,60 +331,42 @@
       <c r="A10" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>18</v>
-      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>19</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>24</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>24</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -414,48 +381,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>32</v>
-      </c>
       <c r="D1" t="s" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>Publisher</t>
+  </si>
+  <si>
+    <t>Jurisdiction</t>
+  </si>
+  <si>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>
@@ -248,7 +254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -345,21 +351,21 @@
       <c r="A12" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>23</v>
       </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
@@ -367,6 +373,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -381,48 +395,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>24</v>
-      </c>
       <c r="E1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2"/>
     </row>

--- a/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -105,13 +105,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice|20231215120000</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R24-TypeActiviteLiberale/FHIR/TRE-R24-TypeActiviteLiberale</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R24-TypeActiviteLiberale/FHIR/TRE-R24-TypeActiviteLiberale|20231215120000</t>
   </si>
   <si>
     <t>L</t>

--- a/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -105,7 +105,7 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice|20260202120000</t>
   </si>
   <si>
     <t/>

--- a/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
+++ b/ig/main/ASS-A24-ModeExercice-TypeActivite-ENREG.xlsx
@@ -105,13 +105,13 @@
     <t>Relationship</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice|20260202120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R24-TypeActiviteLiberale/FHIR/TRE-R24-TypeActiviteLiberale|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R24-TypeActiviteLiberale/FHIR/TRE-R24-TypeActiviteLiberale</t>
   </si>
   <si>
     <t>L</t>
